--- a/AtchisonRegime/Outputs/USA/USA500_Real_Estate/df_regEquityReturns_USA500_Real_Estate.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Real_Estate/df_regEquityReturns_USA500_Real_Estate.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q103"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5716,7 +5716,7 @@
         <v>-1.113652454430497</v>
       </c>
       <c r="C93" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="D93" t="b">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C94" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="D94" t="b">
         <v>0</v>
@@ -5830,7 +5830,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C95" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="D95" t="b">
         <v>0</v>
@@ -5887,7 +5887,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="D96" t="b">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C97" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="D97" t="b">
         <v>0</v>
@@ -6001,7 +6001,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="D98" t="b">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="D99" t="b">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="D100" t="b">
         <v>0</v>
@@ -6172,7 +6172,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="D101" t="b">
         <v>0</v>
@@ -6226,10 +6226,10 @@
         <v>45716</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.8167702922088305</v>
+        <v>-0.8165764810113098</v>
       </c>
       <c r="C102" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="D102" t="b">
         <v>0</v>
@@ -6283,10 +6283,10 @@
         <v>45747</v>
       </c>
       <c r="B103" t="n">
-        <v>-0.7844280456827043</v>
+        <v>-0.836774216411349</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="D103" t="b">
         <v>0</v>
@@ -6333,6 +6333,63 @@
       </c>
       <c r="Q103" t="n">
         <v>139.4050422031683</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B104" t="n">
+        <v>-0.879407738343786</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="D104" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4.50588411890082</v>
+      </c>
+      <c r="G104" t="n">
+        <v>204185.1014496023</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>4.50588411890082</v>
+      </c>
+      <c r="N104" t="n">
+        <v>120.1057895964421</v>
+      </c>
+      <c r="O104" t="n">
+        <v>105.9196482115934</v>
+      </c>
+      <c r="P104" t="n">
+        <v>115.954374849341</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>145.6864718607479</v>
       </c>
     </row>
   </sheetData>
